--- a/output_tcc_var/tabelas/03_teste_johansen.xlsx
+++ b/output_tcc_var/tabelas/03_teste_johansen.xlsx
@@ -473,7 +473,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>55.09292995923461</v>
+        <v>47.9826139843931</v>
       </c>
       <c r="C2" t="n">
         <v>44.4929</v>
@@ -485,7 +485,7 @@
         <v>54.6815</v>
       </c>
       <c r="F2" t="n">
-        <v>26.40672551662735</v>
+        <v>28.11595602579524</v>
       </c>
       <c r="G2" t="n">
         <v>25.1236</v>
@@ -507,7 +507,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.68620444260725</v>
+        <v>19.86665795859785</v>
       </c>
       <c r="C3" t="n">
         <v>27.0669</v>
@@ -519,7 +519,7 @@
         <v>35.4628</v>
       </c>
       <c r="F3" t="n">
-        <v>14.90180025630744</v>
+        <v>11.44732595882066</v>
       </c>
       <c r="G3" t="n">
         <v>18.8928</v>
@@ -541,7 +541,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.78440418629981</v>
+        <v>8.419331999777189</v>
       </c>
       <c r="C4" t="n">
         <v>13.4294</v>
@@ -553,7 +553,7 @@
         <v>19.9349</v>
       </c>
       <c r="F4" t="n">
-        <v>9.850882743594873</v>
+        <v>7.44167745902446</v>
       </c>
       <c r="G4" t="n">
         <v>12.2971</v>
@@ -575,7 +575,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.933521442704941</v>
+        <v>0.9776545407527297</v>
       </c>
       <c r="C5" t="n">
         <v>2.7055</v>
@@ -587,7 +587,7 @@
         <v>6.6349</v>
       </c>
       <c r="F5" t="n">
-        <v>3.933521442704941</v>
+        <v>0.9776545407527297</v>
       </c>
       <c r="G5" t="n">
         <v>2.7055</v>
@@ -609,7 +609,7 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>102.3559549038136</v>
+        <v>102.3492395897118</v>
       </c>
       <c r="C6" t="n">
         <v>44.4929</v>
@@ -621,7 +621,7 @@
         <v>54.6815</v>
       </c>
       <c r="F6" t="n">
-        <v>78.76972533931927</v>
+        <v>78.76310707855033</v>
       </c>
       <c r="G6" t="n">
         <v>25.1236</v>
@@ -643,7 +643,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="n">
-        <v>23.58622956449431</v>
+        <v>23.58613251116149</v>
       </c>
       <c r="C7" t="n">
         <v>27.0669</v>
@@ -655,7 +655,7 @@
         <v>35.4628</v>
       </c>
       <c r="F7" t="n">
-        <v>14.20931213396862</v>
+        <v>14.20941982551742</v>
       </c>
       <c r="G7" t="n">
         <v>18.8928</v>
@@ -677,7 +677,7 @@
         <v>2</v>
       </c>
       <c r="B8" t="n">
-        <v>9.376917430525694</v>
+        <v>9.376712685644065</v>
       </c>
       <c r="C8" t="n">
         <v>13.4294</v>
@@ -689,7 +689,7 @@
         <v>19.9349</v>
       </c>
       <c r="F8" t="n">
-        <v>9.22564723372632</v>
+        <v>9.225515560097442</v>
       </c>
       <c r="G8" t="n">
         <v>12.2971</v>
@@ -711,7 +711,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1512701967993728</v>
+        <v>0.151197125546624</v>
       </c>
       <c r="C9" t="n">
         <v>2.7055</v>
@@ -723,7 +723,7 @@
         <v>6.6349</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1512701967993728</v>
+        <v>0.151197125546624</v>
       </c>
       <c r="G9" t="n">
         <v>2.7055</v>
@@ -745,7 +745,7 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>109.8050542440405</v>
+        <v>109.7998252084616</v>
       </c>
       <c r="C10" t="n">
         <v>44.4929</v>
@@ -757,7 +757,7 @@
         <v>54.6815</v>
       </c>
       <c r="F10" t="n">
-        <v>84.0536210719347</v>
+        <v>84.0485444722171</v>
       </c>
       <c r="G10" t="n">
         <v>25.1236</v>
@@ -779,7 +779,7 @@
         <v>1</v>
       </c>
       <c r="B11" t="n">
-        <v>25.75143317210579</v>
+        <v>25.75128073624453</v>
       </c>
       <c r="C11" t="n">
         <v>27.0669</v>
@@ -791,7 +791,7 @@
         <v>35.4628</v>
       </c>
       <c r="F11" t="n">
-        <v>17.33926998555319</v>
+        <v>17.33935464533987</v>
       </c>
       <c r="G11" t="n">
         <v>18.8928</v>
@@ -813,7 +813,7 @@
         <v>2</v>
       </c>
       <c r="B12" t="n">
-        <v>8.412163186552608</v>
+        <v>8.411926090904657</v>
       </c>
       <c r="C12" t="n">
         <v>13.4294</v>
@@ -825,7 +825,7 @@
         <v>19.9349</v>
       </c>
       <c r="F12" t="n">
-        <v>8.136565737931413</v>
+        <v>8.136415583157016</v>
       </c>
       <c r="G12" t="n">
         <v>12.2971</v>
@@ -847,7 +847,7 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2755974486211948</v>
+        <v>0.2755105077476405</v>
       </c>
       <c r="C13" t="n">
         <v>2.7055</v>
@@ -859,7 +859,7 @@
         <v>6.6349</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2755974486211948</v>
+        <v>0.2755105077476405</v>
       </c>
       <c r="G13" t="n">
         <v>2.7055</v>
@@ -881,7 +881,7 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>93.69058029809931</v>
+        <v>93.68717187539443</v>
       </c>
       <c r="C14" t="n">
         <v>44.4929</v>
@@ -893,7 +893,7 @@
         <v>54.6815</v>
       </c>
       <c r="F14" t="n">
-        <v>65.47471624175903</v>
+        <v>65.47129611658838</v>
       </c>
       <c r="G14" t="n">
         <v>25.1236</v>
@@ -915,7 +915,7 @@
         <v>1</v>
       </c>
       <c r="B15" t="n">
-        <v>28.21586405634028</v>
+        <v>28.21587575880605</v>
       </c>
       <c r="C15" t="n">
         <v>27.0669</v>
@@ -927,7 +927,7 @@
         <v>35.4628</v>
       </c>
       <c r="F15" t="n">
-        <v>19.0876520353532</v>
+        <v>19.08780421484635</v>
       </c>
       <c r="G15" t="n">
         <v>18.8928</v>
@@ -949,7 +949,7 @@
         <v>2</v>
       </c>
       <c r="B16" t="n">
-        <v>9.12821202098708</v>
+        <v>9.12807154395971</v>
       </c>
       <c r="C16" t="n">
         <v>13.4294</v>
@@ -961,7 +961,7 @@
         <v>19.9349</v>
       </c>
       <c r="F16" t="n">
-        <v>9.122324770158913</v>
+        <v>9.122196379342336</v>
       </c>
       <c r="G16" t="n">
         <v>12.2971</v>
@@ -983,7 +983,7 @@
         <v>3</v>
       </c>
       <c r="B17" t="n">
-        <v>0.00588725082816722</v>
+        <v>0.005875164617374321</v>
       </c>
       <c r="C17" t="n">
         <v>2.7055</v>
@@ -995,7 +995,7 @@
         <v>6.6349</v>
       </c>
       <c r="F17" t="n">
-        <v>0.00588725082816722</v>
+        <v>0.005875164617374321</v>
       </c>
       <c r="G17" t="n">
         <v>2.7055</v>
@@ -1017,7 +1017,7 @@
         <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>36.36555054576565</v>
+        <v>37.0751606627888</v>
       </c>
       <c r="C18" t="n">
         <v>44.4929</v>
@@ -1029,7 +1029,7 @@
         <v>54.6815</v>
       </c>
       <c r="F18" t="n">
-        <v>15.8408527406193</v>
+        <v>15.1836480171627</v>
       </c>
       <c r="G18" t="n">
         <v>25.1236</v>
@@ -1051,7 +1051,7 @@
         <v>1</v>
       </c>
       <c r="B19" t="n">
-        <v>20.52469780514635</v>
+        <v>21.8915126456261</v>
       </c>
       <c r="C19" t="n">
         <v>27.0669</v>
@@ -1063,7 +1063,7 @@
         <v>35.4628</v>
       </c>
       <c r="F19" t="n">
-        <v>11.3152777710159</v>
+        <v>11.92703060164254</v>
       </c>
       <c r="G19" t="n">
         <v>18.8928</v>
@@ -1085,7 +1085,7 @@
         <v>2</v>
       </c>
       <c r="B20" t="n">
-        <v>9.209420034130451</v>
+        <v>9.964482043983553</v>
       </c>
       <c r="C20" t="n">
         <v>13.4294</v>
@@ -1097,7 +1097,7 @@
         <v>19.9349</v>
       </c>
       <c r="F20" t="n">
-        <v>8.833451841563745</v>
+        <v>9.821934464766821</v>
       </c>
       <c r="G20" t="n">
         <v>12.2971</v>
@@ -1119,7 +1119,7 @@
         <v>3</v>
       </c>
       <c r="B21" t="n">
-        <v>0.3759681925667052</v>
+        <v>0.1425475792167335</v>
       </c>
       <c r="C21" t="n">
         <v>2.7055</v>
@@ -1131,7 +1131,7 @@
         <v>6.6349</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3759681925667052</v>
+        <v>0.1425475792167335</v>
       </c>
       <c r="G21" t="n">
         <v>2.7055</v>
@@ -1153,7 +1153,7 @@
         <v>0</v>
       </c>
       <c r="B22" t="n">
-        <v>80.38424841759348</v>
+        <v>80.38424841759327</v>
       </c>
       <c r="C22" t="n">
         <v>44.4929</v>
@@ -1165,7 +1165,7 @@
         <v>54.6815</v>
       </c>
       <c r="F22" t="n">
-        <v>47.28765795537901</v>
+        <v>47.2876579553788</v>
       </c>
       <c r="G22" t="n">
         <v>25.1236</v>
@@ -1199,7 +1199,7 @@
         <v>35.4628</v>
       </c>
       <c r="F23" t="n">
-        <v>19.6438152260224</v>
+        <v>19.64381522602237</v>
       </c>
       <c r="G23" t="n">
         <v>18.8928</v>
@@ -1221,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="B24" t="n">
-        <v>13.45277523619206</v>
+        <v>13.45277523619209</v>
       </c>
       <c r="C24" t="n">
         <v>13.4294</v>
@@ -1255,7 +1255,7 @@
         <v>3</v>
       </c>
       <c r="B25" t="n">
-        <v>2.685029556784182</v>
+        <v>2.685029556784212</v>
       </c>
       <c r="C25" t="n">
         <v>2.7055</v>
@@ -1267,7 +1267,7 @@
         <v>6.6349</v>
       </c>
       <c r="F25" t="n">
-        <v>2.685029556784182</v>
+        <v>2.685029556784212</v>
       </c>
       <c r="G25" t="n">
         <v>2.7055</v>
@@ -1289,7 +1289,7 @@
         <v>0</v>
       </c>
       <c r="B26" t="n">
-        <v>57.19404469483058</v>
+        <v>57.1940446948304</v>
       </c>
       <c r="C26" t="n">
         <v>44.4929</v>
@@ -1301,7 +1301,7 @@
         <v>54.6815</v>
       </c>
       <c r="F26" t="n">
-        <v>38.05549517182224</v>
+        <v>38.05549517182205</v>
       </c>
       <c r="G26" t="n">
         <v>25.1236</v>
@@ -1323,7 +1323,7 @@
         <v>1</v>
       </c>
       <c r="B27" t="n">
-        <v>19.13854952300833</v>
+        <v>19.13854952300836</v>
       </c>
       <c r="C27" t="n">
         <v>27.0669</v>
@@ -1335,7 +1335,7 @@
         <v>35.4628</v>
       </c>
       <c r="F27" t="n">
-        <v>12.07945709259508</v>
+        <v>12.07945709259505</v>
       </c>
       <c r="G27" t="n">
         <v>18.8928</v>
@@ -1357,7 +1357,7 @@
         <v>2</v>
       </c>
       <c r="B28" t="n">
-        <v>7.059092430413249</v>
+        <v>7.059092430413311</v>
       </c>
       <c r="C28" t="n">
         <v>13.4294</v>
@@ -1369,7 +1369,7 @@
         <v>19.9349</v>
       </c>
       <c r="F28" t="n">
-        <v>6.664121760729738</v>
+        <v>6.664121760729769</v>
       </c>
       <c r="G28" t="n">
         <v>12.2971</v>
@@ -1391,7 +1391,7 @@
         <v>3</v>
       </c>
       <c r="B29" t="n">
-        <v>0.3949706696835118</v>
+        <v>0.3949706696835419</v>
       </c>
       <c r="C29" t="n">
         <v>2.7055</v>
@@ -1403,7 +1403,7 @@
         <v>6.6349</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3949706696835118</v>
+        <v>0.3949706696835419</v>
       </c>
       <c r="G29" t="n">
         <v>2.7055</v>
@@ -1425,7 +1425,7 @@
         <v>0</v>
       </c>
       <c r="B30" t="n">
-        <v>63.15289655544966</v>
+        <v>63.15289655544959</v>
       </c>
       <c r="C30" t="n">
         <v>44.4929</v>
@@ -1437,7 +1437,7 @@
         <v>54.6815</v>
       </c>
       <c r="F30" t="n">
-        <v>42.06495198289691</v>
+        <v>42.06495198289684</v>
       </c>
       <c r="G30" t="n">
         <v>25.1236</v>
@@ -1471,7 +1471,7 @@
         <v>35.4628</v>
       </c>
       <c r="F31" t="n">
-        <v>15.78952758277165</v>
+        <v>15.78952758277174</v>
       </c>
       <c r="G31" t="n">
         <v>18.8928</v>
@@ -1493,7 +1493,7 @@
         <v>2</v>
       </c>
       <c r="B32" t="n">
-        <v>5.298416989781094</v>
+        <v>5.298416989781002</v>
       </c>
       <c r="C32" t="n">
         <v>13.4294</v>
@@ -1505,7 +1505,7 @@
         <v>19.9349</v>
       </c>
       <c r="F32" t="n">
-        <v>5.193812952135609</v>
+        <v>5.193812952135517</v>
       </c>
       <c r="G32" t="n">
         <v>12.2971</v>
